--- a/extenbooks/S517.xlsx
+++ b/extenbooks/S517.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>BEA, units=billions_usd</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>BEA, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BEA, units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -477,804 +489,1092 @@
           <t>S517-A</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S517-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S517-EXT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1925</v>
+        <v>1948</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>126.977</v>
+        <v>291.557</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>291.557</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1926</v>
+        <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>131.537</v>
+        <v>296.671</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>296.671</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1927</v>
+        <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>134.175</v>
+        <v>335.868</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>335.868</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1928</v>
+        <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>137.774</v>
+        <v>366.226</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>366.226</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1929</v>
+        <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>137.07</v>
+        <v>386.31</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1930</v>
+        <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>130.22</v>
+        <v>403.718</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>403.718</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1931</v>
+        <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>116.244</v>
+        <v>414.924</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>414.924</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1932</v>
+        <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>107.642</v>
+        <v>457.052</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>457.052</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1933</v>
+        <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>109.278</v>
+        <v>505.534</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>505.534</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1934</v>
+        <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>110.648</v>
+        <v>540.636</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>540.636</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1935</v>
+        <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>110.315</v>
+        <v>551.356</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>551.356</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1936</v>
+        <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>121.36</v>
+        <v>573.9589999999999</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>573.9589999999999</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1937</v>
+        <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>126.498</v>
+        <v>586.872</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>586.872</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1938</v>
+        <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>125.187</v>
+        <v>604.328</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>604.328</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1939</v>
+        <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>125.5</v>
+        <v>626.795</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>626.795</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1940</v>
+        <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>133.587</v>
+        <v>650.603</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>650.603</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1941</v>
+        <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>150.956</v>
+        <v>689.318</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>689.318</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1942</v>
+        <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>160.521</v>
+        <v>738.843</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>738.843</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1943</v>
+        <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>163.319</v>
+        <v>804.263</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>804.263</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1944</v>
+        <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>165.236</v>
+        <v>871.188</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>871.188</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1945</v>
+        <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>180.207</v>
+        <v>957.886</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>957.886</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1946</v>
+        <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>221.007</v>
+        <v>1055.775</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1055.775</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1947</v>
+        <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>265.725</v>
+        <v>1161.635</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1161.635</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1948</v>
+        <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>291.557</v>
+        <v>1275.119</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1275.119</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1949</v>
+        <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>296.671</v>
+        <v>1385.696</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1385.696</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1950</v>
+        <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>335.868</v>
+        <v>1560.649</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1560.649</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1951</v>
+        <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>366.226</v>
+        <v>1893.965</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1893.965</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1952</v>
+        <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>386.31</v>
+        <v>2083.536</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2083.536</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1953</v>
+        <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>403.718</v>
+        <v>2280.237</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2280.237</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1954</v>
+        <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>414.924</v>
+        <v>2532.629</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2532.629</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1955</v>
+        <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>457.052</v>
+        <v>2870.135</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>2870.135</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1956</v>
+        <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>505.534</v>
+        <v>3313.954</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3313.954</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1957</v>
+        <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>540.636</v>
+        <v>3800.29</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>3800.29</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1958</v>
+        <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>551.356</v>
+        <v>4300.221</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>4300.221</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1959</v>
+        <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>573.9589999999999</v>
+        <v>4589.165</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>4589.165</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1960</v>
+        <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>586.872</v>
+        <v>4744.723</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>4744.723</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1961</v>
+        <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>604.328</v>
+        <v>5040.975</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>5040.975</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1962</v>
+        <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>626.795</v>
+        <v>5332.407</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>5332.407</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1963</v>
+        <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>650.603</v>
+        <v>5603.761</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>5603.761</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1964</v>
+        <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>689.318</v>
+        <v>5919.104</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>5919.104</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1965</v>
+        <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>738.843</v>
+        <v>6311.228</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>6311.228</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1966</v>
+        <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>804.263</v>
+        <v>6699.84</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>6699.84</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1967</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>871.188</v>
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>7071.254</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>7071.254</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1968</v>
+        <v>1991</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>957.886</v>
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>7242.497</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>7242.497</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1969</v>
+        <v>1992</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>1055.775</v>
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>7487.351</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>7487.351</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1970</v>
+        <v>1993</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1161.635</v>
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>7838.125</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>7838.125</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1971</v>
+        <v>1994</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>1275.119</v>
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>8273.204</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>8273.204</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1972</v>
+        <v>1995</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>1385.696</v>
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>8723.558000000001</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>8723.558000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1973</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>1560.649</v>
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>9152.132</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>9152.132</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1974</v>
+        <v>1997</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>1893.965</v>
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>9674.473</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>9674.473</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1975</v>
+        <v>1998</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>2083.536</v>
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>10226.721</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>10226.721</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1976</v>
+        <v>1999</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2280.237</v>
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>10849.249</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>10849.249</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1977</v>
+        <v>2000</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>2532.629</v>
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>11607.864</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>11607.864</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1978</v>
+        <v>2001</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>2870.135</v>
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>12189.396</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>12189.396</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1979</v>
+        <v>2002</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>3313.954</v>
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>12616.326</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>12616.326</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>3800.29</v>
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>13038.217</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>13038.217</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1981</v>
+        <v>2004</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>4300.221</v>
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>14152.545</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>14152.545</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1982</v>
+        <v>2005</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>4589.165</v>
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>15429.476</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>15429.476</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1983</v>
+        <v>2006</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>4744.723</v>
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>16706.002</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>16706.002</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1984</v>
+        <v>2007</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>5040.975</v>
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>17647.597</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>17647.597</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1985</v>
+        <v>2008</v>
       </c>
       <c r="B63" s="3" t="n">
-        <v>5332.407</v>
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>18787.982</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>18787.982</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1986</v>
+        <v>2009</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>5603.761</v>
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>18233.843</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>18233.843</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1987</v>
+        <v>2010</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>5919.104</v>
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>18681.707</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>18681.707</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1988</v>
+        <v>2011</v>
       </c>
       <c r="B66" s="3" t="n">
-        <v>6311.228</v>
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>19549.432</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>19549.432</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1989</v>
+        <v>2012</v>
       </c>
       <c r="B67" s="3" t="n">
-        <v>6699.84</v>
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>20201.795</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>20201.795</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1990</v>
+        <v>2013</v>
       </c>
       <c r="B68" s="3" t="n">
-        <v>7071.254</v>
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>21039.791</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>21039.791</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1991</v>
+        <v>2014</v>
       </c>
       <c r="B69" s="3" t="n">
-        <v>7242.497</v>
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>22022.201</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>22022.201</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1992</v>
+        <v>2015</v>
       </c>
       <c r="B70" s="3" t="n">
-        <v>7487.351</v>
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>22494.315</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>22494.315</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1993</v>
+        <v>2016</v>
       </c>
       <c r="B71" s="3" t="n">
-        <v>7838.125</v>
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>23161.992</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>23161.992</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1994</v>
+        <v>2017</v>
       </c>
       <c r="B72" s="3" t="n">
-        <v>8273.204</v>
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>24066.902</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>24066.902</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1995</v>
+        <v>2018</v>
       </c>
       <c r="B73" s="3" t="n">
-        <v>8723.558000000001</v>
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>25227.313</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>25227.313</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1996</v>
+        <v>2019</v>
       </c>
       <c r="B74" s="3" t="n">
-        <v>9152.132</v>
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>26423.854</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>26423.854</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1997</v>
+        <v>2020</v>
       </c>
       <c r="B75" s="3" t="n">
-        <v>9674.473</v>
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>27010.148</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>27010.148</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1998</v>
+        <v>2021</v>
       </c>
       <c r="B76" s="3" t="n">
-        <v>10226.721</v>
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>30051.849</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>30051.849</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1999</v>
+        <v>2022</v>
       </c>
       <c r="B77" s="3" t="n">
-        <v>10849.249</v>
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>33673.661</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>33673.661</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="B78" s="3" t="n">
-        <v>11607.864</v>
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>34771.025</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>34771.025</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="B79" s="3" t="n">
-        <v>12189.396</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B80" s="3" t="n">
-        <v>12616.326</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>13038.217</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B82" s="3" t="n">
-        <v>14152.545</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>15429.476</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>16706.002</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>17647.597</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>18787.982</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>18233.843</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>18681.707</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>19549.432</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>20201.795</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>21039.791</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>22022.201</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B93" s="3" t="n">
-        <v>22494.315</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>23161.992</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>24066.902</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>25227.313</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B97" s="3" t="n">
-        <v>26423.854</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B98" s="3" t="n">
-        <v>27010.148</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>30051.849</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B100" s="3" t="n">
-        <v>33673.661</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>34771.025</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B102" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>35899.94</v>
+      </c>
+      <c r="D79" s="3" t="n">
         <v>35899.94</v>
       </c>
     </row>
@@ -1289,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1350,7 +1650,11 @@
           <t>Book Table</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Appendix_H_K_net_stock_fixed_capital</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1384,7 +1688,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>None–None</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1700,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1710,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_5_5, Fig_5_8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1446,66 +1754,87 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S517-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S517-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S517-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S517 — Productive Capital Stock (K*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 supporting. **Period**: 1925-2024. **Units**: billions_usd.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t># S517 — Productive Capital Stock (K*)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Status**: validated_book_and_extension</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>K* is the productive constant capital STOCK — the accumulated past production that sits behind each year's productive activity. Distinguished from Mp (S502, constant capital FLOW = depreciation + materials used).</t>
+          <t>**Chapter**: 5 supporting. **Period**: 1925-2024. **Units**: billions_usd.</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1846,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1858,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BEA Fixed Assets Table 4.1 (cached at `data/raw/bea/fixed_assets_4_1_net_stock.csv`), Line 1: "Private nonresidential fixed assets". 100 years (1925-2024).</t>
+          <t>K* is the productive constant capital STOCK — the accumulated past production that sits behind each year's productive activity. Distinguished from Mp (S502, constant capital FLOW = depreciation + materials used).</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1870,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>## Productive partition note</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1882,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Line 1 is TOTAL private nonresidential fixed assets — includes both productive and a small unproductive (financial-sector real estate) component. Standard first-pass K*. A refinement (per IMPLEMENTATION_PLAN.md Phase 2.A) would subtract Line 33 (Financial sector, ~5-10% of total) to get a more faithful productive K*.</t>
+          <t>BEA Fixed Assets Table 4.1 (cached at `data/raw/bea/fixed_assets_4_1_net_stock.csv`), Line 1: "Private nonresidential fixed assets". 100 years (1925-2024).</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1894,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>## Endpoints</t>
+          <t>## Productive partition note</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1906,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1948 = $292B, 1989 = $6,700B, 2024 = $35,900B. Validator PASS (range + monotonic).</t>
+          <t>Line 1 is TOTAL private nonresidential fixed assets — includes both productive and a small unproductive (financial-sector real estate) component. Standard first-pass K*. A refinement (per IMPLEMENTATION_PLAN.md Phase 2.A) would subtract Line 33 (Financial sector, ~5-10% of total) to get a more faithful productive K*.</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1918,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>## Unblocks</t>
+          <t>## Endpoints</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1930,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S510 (K/V*), S513 (r*), S514 (r*_adj), and the activation of AS001 (Social Burden Rate).</t>
+          <t>1948 = $292B, 1989 = $6,700B, 2024 = $35,900B. Validator PASS (range + monotonic).</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1942,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>## Unblocks</t>
         </is>
       </c>
     </row>
@@ -1624,6 +1953,30 @@
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
+        <is>
+          <t>S510 (K/V*), S513 (r*), S514 (r*_adj), and the activation of AS001 (Social Burden Rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1640,13 +1993,364 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No research JSON for S517</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>entry_id_or_type</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>content_or_quote</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>source_ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>the Marxian general rate of profit r*, defined here as the ratio of surplus value to total fixed capital K</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ST_1994, p. 122, Section 5.5 opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>More properly, one should add the stock of circulating capital (i.e., inventories of raw materials and goods in process, which are the stock equivalents of C* and V*, or M and W in the orthodox case) to the stock of fixed capital. But consistent data on the former are not readily available.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ST_1994, p. 122, Section 5.5 Footnote 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>We also estimate the value composition of (fixed) capital C*/V* = K/V*, as well as the materialized composition of (fixed) capital C*/(V* + S*) = K/(V* + S*). All variables are in current dollars, including the capital stock that is measured at current replacement costs.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ST_1994, p. 122, Section 5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all measured ratios are adjusted for cyclical fluctuations by means of a measure of capacity utilization developed in Shaikh (1987, 1992a).</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ST_1994, p. 124, Section 5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The Marxian general rate of profit r*, defined here as the ratio of surplus value to total fixed capital K.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>More properly, one should add the stock of circulating capital (i.e., inventories of raw materials and goods in process, which are the stock equivalents of C* and V*, or M and W in the orthodox case) to the stock of fixed capital. But consistent data on the former are not readily available.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>All variables are in current dollars, including the capital stock that is measured at current replacement costs.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S517 measures the Productive Capital Stock (K*) — the fixed capital stock employed in productive sectors. In the Shaikh-Tonak framework, this is the capital stock corresponding to sectors that produce use-values and surplus value (agriculture, mining, construction, manufacturing, transportation, communications, utilities, and trade).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>series_registry.json (S517 definition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Registry specifies a single construction step: load subseries S517-A, which is 'BEA Fixed Assets 4.1 Line 1' covering 1925-2024 in billions of USD. The loader is L01 and processor is P02. Wave 2 assignment indicates this is a foundational series loaded early in the pipeline.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>series_registry.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S517-A sources from BEA Fixed Assets Table 4.1, Line 1 — Current-Cost Net Stock of Private Fixed Assets. This table provides the net stock of private fixed assets by industry. The productive capital stock requires filtering to productive industries only (per the Shaikh-Tonak sector classification).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>series_registry.json subseries S517-A; BEA Fixed Assets tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K* enters profit rate calculations as the denominator: r = S*/K* (the Marxian general rate of profit). It also appears in capital-output ratios and organic composition of capital. Chapter 5 develops these measures as part of the overall framework for measuring the wealth of nations.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 and Ch9 profit rate analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>No extension is specified (extension: null) — the BEA Fixed Assets data already extends to 2024, providing continuous modern coverage. Status is book_period_validated.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>series_registry.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Productive Capital Stock (K*) loaded from BEA Fixed Assets Table 4.1 Line 1 (1925-2024). Used in profit rate calculations as the capital denominator (r = S*/K*).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sector filtering for productive-only industries not yet documented in detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets industry classifications may differ from the original 85 IO sectors used in the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S501</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S505</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BEA_FixedAssets</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bureau of Economic Analysis. Fixed Assets Accounts Tables. Table 4.1: Current-Cost Net Stock of Private Fixed Assets by Industry. https://apps.bea.gov/iTable/</t>
         </is>
       </c>
     </row>
@@ -1661,11 +2365,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1717,14 +2421,178 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>null — series does not extend beyond book period</t>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>splice_year</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>splice_method</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S517-EXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S517-COMBINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rescale_factor</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>extension_period</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[1990, 2024]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5 (The Marxian Categories: Empirical Estimates), Appendix H (K* net stock of fixed capital, text-only in published volume)", "shaikh_appendix_ref": "Appendix H tabulated K* endpoints (Appendix H is text-only per RMWND CLAUDE.md and is not extracted in the current KB build); cross-reference Table 5.8 / 5.9 (K* = C*f reporting convention, billions of current dollars) and Figures 5.5 and 5.8 (K* plotted in r* construction)", "extension_source": "BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock; pre-cached at Inputs/ST2/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: Inputs/ST2/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)", "extension_url": "https://apps.bea.gov/iTable/?reqid=10&amp;step=2&amp;isuri=1 (Fixed Assets, Table 4.1); API endpoint: https://apps.bea.gov/api/data?UserID=&lt;KEY&gt;&amp;method=GetData&amp;datasetname=FixedAssets&amp;TableName=FAAt401&amp;Frequency=A&amp;Year=ALL&amp;ResultFormat=JSON", "conceptual_continuity": "Productive Capital Stock K* is the current-cost net stock of fixed capital deployed in the productive economy. Both the book period (1948-1989) and the extension (1990-2024) draw on the same BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, Current-Cost Net Stock) \u2014 i.e., the underlying source series is identical across the seam. The splice is therefore trivial: splice_method=level at 1989 with rescale_factor=1.0, because there is no series-change discontinuity to bridge. The only methodological caveat (shared with the book period itself) is that Table 4.1 Line 1 is aggregate private nonresidential \u2014 it is not yet filtered through the 85-IO productive concordance to subtract the financial-sector component (estimated ~5-10%). This concordance refinement is a future Stage 5 task (see IMPLEMENTATION_PLAN.md Phase 2.A); for now the aggregate is used in both eras, which preserves comparability across the splice but biases the level upward relative to a strict productive subset.", "vintage_note": "BEA API pull dated 2026-02-24 (per Inputs/ST2/Inputs/API_Data/BEA/provenance_fixed_assets.json). Book-period reference values are frozen at the book's publication vintage in principle, but the operational book reference for S517 is the same modern BEA Table 4.1 series used for the extension (because the book's Appendix H values are not yet extracted from the text-only appendix). BEA Fixed Assets undergoes periodic comprehensive revisions; the cached 2026-02-24 pull represents the most recent vintage at the time of construction. For strict gross-stock replication (book Table 5.8 specifies K* = gross stock), BEA Table 4.2 (Current-Cost Gross Stock) would be the alternative source; not yet pulled.", "note": "Stage 5 cohort 3 extension patch per Decision 0003 binary-invariant rule. Book and extension share the same source, making this a degenerate-but-honest level splice (rescale_factor=1.0)."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1925": 126.977, "1948": 291.557, "1958": 551.356, "1967": 871.188, "1980": 3800.29, "1989": 6699.84}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[100.0, 20000.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>reference_values_units</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>billions of current dollars (current-cost net stock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>reference_values_source</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock — pre-cached at Inputs/ST2/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: Inputs/ST2/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S517.xlsx
+++ b/extenbooks/S517.xlsx
@@ -1589,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1918,7 +1918,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>## Endpoints</t>
+          <t>## Gross-vs-net disclosure (v1.1 Phase 5)</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1948 = $292B, 1989 = $6,700B, 2024 = $35,900B. Validator PASS (range + monotonic).</t>
+          <t>&gt; **Note**: ST 1994 prose calls K* "gross capital stock" (e.g., Table 5.8 header), but published values match BEA Fixed Assets Table 4.1 **NET** stock exactly at all 5 benchmark years (1948 = 292, 1958 = 551, 1967 = 871, 1980 = 3 800, 1989 = 6 700 $B). The book's terminology is in error; the implementation is net stock. BEA publishes no current-cost gross stock for private nonresidential fixed assets. See `Technical/DIVERGENCE_REGISTER.json` entry **DIV-008** for the full divergence record.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>## Unblocks</t>
+          <t>## Endpoints</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S510 (K/V*), S513 (r*), S514 (r*_adj), and the activation of AS001 (Social Burden Rate).</t>
+          <t>1948 = $292B, 1989 = $6,700B, 2024 = $35,900B. Validator PASS (range + monotonic).</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>## Unblocks</t>
         </is>
       </c>
     </row>
@@ -1977,6 +1977,30 @@
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
+        <is>
+          <t>S510 (K/V*), S513 (r*), S514 (r*_adj), and the activation of XS001 (Social Burden Rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -2365,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2556,43 +2580,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"1925": 126.977, "1948": 291.557, "1958": 551.356, "1967": 871.188, "1980": 3800.29, "1989": 6699.84}</t>
+          <t>{"1948": 291.557, "1958": 551.356, "1967": 871.188, "1980": 3800.29, "1989": 6699.84}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>v1.3_patch</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[100.0, 20000.0]</t>
+          <t>DIV-027: removed the spurious 1925 benchmark (126.977). S517 covers 1948+ on NET stock; the series never produces a 1925 value, so the benchmark was always MISSING. All 5 in-range anchors PASS. NET-vs-gross K* convention switch deferred to v1.4 (not changed here).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reference_values_units</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>billions of current dollars (current-cost net stock)</t>
+          <t>[100.0, 20000.0]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>reference_values_units</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>billions of current dollars (current-cost net stock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>reference_values_source</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock — pre-cached at Inputs/ST2/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: Inputs/ST2/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S517.xlsx
+++ b/extenbooks/S517.xlsx
@@ -447,19 +447,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>S517 — Productive Capital Stock (K*)</t>
+          <t>S517 — Productive Capital Stock (K*; BEA net current-cost, primary)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -473,6 +476,21 @@
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>BEA, units=billions_usd</t>
         </is>
@@ -495,6 +513,21 @@
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S517-EXBOTH</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S517-EXFIN</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>S517-EXIPP</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>S517-EXT</t>
         </is>
@@ -511,6 +544,15 @@
         <v>291.557</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>273.251</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>284.584</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>280.216</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -525,6 +567,15 @@
         <v>296.671</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>278.576</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>290.223</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>285.016</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -539,6 +590,15 @@
         <v>335.868</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>315.896</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>328.705</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>323.051</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -553,6 +613,15 @@
         <v>366.226</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>344.299</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>357.897</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>352.619</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -567,6 +636,15 @@
         <v>386.31</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v>362.984</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>377.605</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>371.679</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -581,6 +659,15 @@
         <v>403.718</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>378.597</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>394.814</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>387.489</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -595,6 +682,15 @@
         <v>414.924</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>388.365</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>406.033</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>397.242</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -609,6 +705,15 @@
         <v>457.052</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v>427.58</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>447.126</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>437.491</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -623,6 +728,15 @@
         <v>505.534</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>472.008</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>494.093</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>483.433</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -637,6 +751,15 @@
         <v>540.636</v>
       </c>
       <c r="D12" s="3" t="n">
+        <v>504.039</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>528.442</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>516.217</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -651,6 +774,15 @@
         <v>551.356</v>
       </c>
       <c r="D13" s="3" t="n">
+        <v>512.386</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>538.769</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>524.958</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -665,6 +797,15 @@
         <v>573.9589999999999</v>
       </c>
       <c r="D14" s="3" t="n">
+        <v>531.848</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>560.807</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>544.984</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -679,6 +820,15 @@
         <v>586.872</v>
       </c>
       <c r="D15" s="3" t="n">
+        <v>542.0410000000001</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>573.154</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>555.722</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -693,6 +843,15 @@
         <v>604.328</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>556.16</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>589.769</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>570.662</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -707,6 +866,15 @@
         <v>626.795</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>575.365</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>611.175</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>590.905</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -721,6 +889,15 @@
         <v>650.603</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v>595.244</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>634.022</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>611.71</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -735,6 +912,15 @@
         <v>689.318</v>
       </c>
       <c r="D19" s="3" t="n">
+        <v>629.258</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>670.972</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>647.417</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -749,6 +935,15 @@
         <v>738.843</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v>673.111</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>718.658</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>693.033</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -763,6 +958,15 @@
         <v>804.263</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v>731.792</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>781.936</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>753.773</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -777,6 +981,15 @@
         <v>871.188</v>
       </c>
       <c r="D22" s="3" t="n">
+        <v>790.643</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>846.522</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>814.849</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -791,6 +1004,15 @@
         <v>957.886</v>
       </c>
       <c r="D23" s="3" t="n">
+        <v>867.145</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>929.389</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>895.047</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -805,6 +1027,15 @@
         <v>1055.775</v>
       </c>
       <c r="D24" s="3" t="n">
+        <v>953.481</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1023.223</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>985.265</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -819,6 +1050,15 @@
         <v>1161.635</v>
       </c>
       <c r="D25" s="3" t="n">
+        <v>1048.579</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1125.131</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1084.104</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -833,6 +1073,15 @@
         <v>1275.119</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v>1152.113</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1233.452</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1192.612</v>
+      </c>
+      <c r="G26" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -847,6 +1096,15 @@
         <v>1385.696</v>
       </c>
       <c r="D27" s="3" t="n">
+        <v>1251.575</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1338.913</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1297.028</v>
+      </c>
+      <c r="G27" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -861,6 +1119,15 @@
         <v>1560.649</v>
       </c>
       <c r="D28" s="3" t="n">
+        <v>1409.57</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1506.325</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1462.2</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -875,6 +1142,15 @@
         <v>1893.965</v>
       </c>
       <c r="D29" s="3" t="n">
+        <v>1716.328</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1825.898</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1782.038</v>
+      </c>
+      <c r="G29" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -889,6 +1165,15 @@
         <v>2083.536</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v>1887.894</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2006.303</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1962.059</v>
+      </c>
+      <c r="G30" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -903,6 +1188,15 @@
         <v>2280.237</v>
       </c>
       <c r="D31" s="3" t="n">
+        <v>2063.892</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2193.056</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>2147.301</v>
+      </c>
+      <c r="G31" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -917,6 +1211,15 @@
         <v>2532.629</v>
       </c>
       <c r="D32" s="3" t="n">
+        <v>2291.501</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>2433.203</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2386.795</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -931,6 +1234,15 @@
         <v>2870.135</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v>2595.361</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>2753.931</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>2706.974</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -945,6 +1257,15 @@
         <v>3313.954</v>
       </c>
       <c r="D34" s="3" t="n">
+        <v>2992.187</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>3173.589</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>3127.111</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -959,6 +1280,15 @@
         <v>3800.29</v>
       </c>
       <c r="D35" s="3" t="n">
+        <v>3424.281</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>3631.85</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>3586.447</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -973,6 +1303,15 @@
         <v>4300.221</v>
       </c>
       <c r="D36" s="3" t="n">
+        <v>3865.182</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>4102.933</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>4055.3</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -987,6 +1326,15 @@
         <v>4589.165</v>
       </c>
       <c r="D37" s="3" t="n">
+        <v>4100.097</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>4365.643</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4315.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1001,6 +1349,15 @@
         <v>4744.723</v>
       </c>
       <c r="D38" s="3" t="n">
+        <v>4204.282</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>4498.446</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>4440.663</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1015,6 +1372,15 @@
         <v>5040.975</v>
       </c>
       <c r="D39" s="3" t="n">
+        <v>4435.945</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>4762.827</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>4702.52</v>
+      </c>
+      <c r="G39" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1029,6 +1395,15 @@
         <v>5332.407</v>
       </c>
       <c r="D40" s="3" t="n">
+        <v>4658.511</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>5017.886</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>4959.79</v>
+      </c>
+      <c r="G40" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1043,6 +1418,15 @@
         <v>5603.761</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v>4855.281</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5246.679</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>5197.354</v>
+      </c>
+      <c r="G41" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1057,6 +1441,15 @@
         <v>5919.104</v>
       </c>
       <c r="D42" s="3" t="n">
+        <v>5090.543</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>5521.851</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>5470.379</v>
+      </c>
+      <c r="G42" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1071,6 +1464,15 @@
         <v>6311.228</v>
       </c>
       <c r="D43" s="3" t="n">
+        <v>5397.477</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>5868.384</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>5819.773</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1085,6 +1487,15 @@
         <v>6699.84</v>
       </c>
       <c r="D44" s="3" t="n">
+        <v>5691.824</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>6207.914</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>6159.295</v>
+      </c>
+      <c r="G44" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1099,6 +1510,15 @@
         <v>7071.254</v>
       </c>
       <c r="D45" s="3" t="n">
+        <v>5972.754</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>6535.902</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>6478.995</v>
+      </c>
+      <c r="G45" s="3" t="n">
         <v>7071.254</v>
       </c>
     </row>
@@ -1113,6 +1533,15 @@
         <v>7242.497</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>6075.412</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>6685.675</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>6598.864</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>7242.497</v>
       </c>
     </row>
@@ -1127,6 +1556,15 @@
         <v>7487.351</v>
       </c>
       <c r="D47" s="3" t="n">
+        <v>6251.598</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>6905.813</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>6795.622</v>
+      </c>
+      <c r="G47" s="3" t="n">
         <v>7487.351</v>
       </c>
     </row>
@@ -1141,6 +1579,15 @@
         <v>7838.125</v>
       </c>
       <c r="D48" s="3" t="n">
+        <v>6528.25</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>7223.847</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>7101.482</v>
+      </c>
+      <c r="G48" s="3" t="n">
         <v>7838.125</v>
       </c>
     </row>
@@ -1155,6 +1602,15 @@
         <v>8273.204</v>
       </c>
       <c r="D49" s="3" t="n">
+        <v>6869.243</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>7617.137</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>7482.039</v>
+      </c>
+      <c r="G49" s="3" t="n">
         <v>8273.204</v>
       </c>
     </row>
@@ -1169,6 +1625,15 @@
         <v>8723.558000000001</v>
       </c>
       <c r="D50" s="3" t="n">
+        <v>7228.784</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>8035.875</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>7872.569</v>
+      </c>
+      <c r="G50" s="3" t="n">
         <v>8723.558000000001</v>
       </c>
     </row>
@@ -1183,6 +1648,15 @@
         <v>9152.132</v>
       </c>
       <c r="D51" s="3" t="n">
+        <v>7562.641</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>8430.442999999999</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>8240.013999999999</v>
+      </c>
+      <c r="G51" s="3" t="n">
         <v>9152.132</v>
       </c>
     </row>
@@ -1197,6 +1671,15 @@
         <v>9674.473</v>
       </c>
       <c r="D52" s="3" t="n">
+        <v>7963.688</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>8912.296</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>8680.664000000001</v>
+      </c>
+      <c r="G52" s="3" t="n">
         <v>9674.473</v>
       </c>
     </row>
@@ -1211,6 +1694,15 @@
         <v>10226.721</v>
       </c>
       <c r="D53" s="3" t="n">
+        <v>8373.396000000001</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>9404.959999999999</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>9144.07</v>
+      </c>
+      <c r="G53" s="3" t="n">
         <v>10226.721</v>
       </c>
     </row>
@@ -1225,6 +1717,15 @@
         <v>10849.249</v>
       </c>
       <c r="D54" s="3" t="n">
+        <v>8814.712</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>9960.377</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>9642.474</v>
+      </c>
+      <c r="G54" s="3" t="n">
         <v>10849.249</v>
       </c>
     </row>
@@ -1239,6 +1740,15 @@
         <v>11607.864</v>
       </c>
       <c r="D55" s="3" t="n">
+        <v>9394.83</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>10657.874</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>10272.756</v>
+      </c>
+      <c r="G55" s="3" t="n">
         <v>11607.864</v>
       </c>
     </row>
@@ -1253,6 +1763,15 @@
         <v>12189.396</v>
       </c>
       <c r="D56" s="3" t="n">
+        <v>9884.598</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>11201.686</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>10794.156</v>
+      </c>
+      <c r="G56" s="3" t="n">
         <v>12189.396</v>
       </c>
     </row>
@@ -1267,6 +1786,15 @@
         <v>12616.326</v>
       </c>
       <c r="D57" s="3" t="n">
+        <v>10235.099</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>11596.512</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>11172.304</v>
+      </c>
+      <c r="G57" s="3" t="n">
         <v>12616.326</v>
       </c>
     </row>
@@ -1281,6 +1809,15 @@
         <v>13038.217</v>
       </c>
       <c r="D58" s="3" t="n">
+        <v>10556.782</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>11992.387</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>11516.597</v>
+      </c>
+      <c r="G58" s="3" t="n">
         <v>13038.217</v>
       </c>
     </row>
@@ -1295,6 +1832,15 @@
         <v>14152.545</v>
       </c>
       <c r="D59" s="3" t="n">
+        <v>11523.611</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>13023.492</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>12561.907</v>
+      </c>
+      <c r="G59" s="3" t="n">
         <v>14152.545</v>
       </c>
     </row>
@@ -1309,6 +1855,15 @@
         <v>15429.476</v>
       </c>
       <c r="D60" s="3" t="n">
+        <v>12616.261</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>14217.62</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>13734.052</v>
+      </c>
+      <c r="G60" s="3" t="n">
         <v>15429.476</v>
       </c>
     </row>
@@ -1323,6 +1878,15 @@
         <v>16706.002</v>
       </c>
       <c r="D61" s="3" t="n">
+        <v>13710.829</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>15410.979</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>14908.784</v>
+      </c>
+      <c r="G61" s="3" t="n">
         <v>16706.002</v>
       </c>
     </row>
@@ -1337,6 +1901,15 @@
         <v>17647.597</v>
       </c>
       <c r="D62" s="3" t="n">
+        <v>14471.278</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>16291.401</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>15723.248</v>
+      </c>
+      <c r="G62" s="3" t="n">
         <v>17647.597</v>
       </c>
     </row>
@@ -1351,6 +1924,15 @@
         <v>18787.982</v>
       </c>
       <c r="D63" s="3" t="n">
+        <v>15451.003</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>17367.16</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>16759.893</v>
+      </c>
+      <c r="G63" s="3" t="n">
         <v>18787.982</v>
       </c>
     </row>
@@ -1365,6 +1947,15 @@
         <v>18233.843</v>
       </c>
       <c r="D64" s="3" t="n">
+        <v>14909.181</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>16874.895</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>16149.385</v>
+      </c>
+      <c r="G64" s="3" t="n">
         <v>18233.843</v>
       </c>
     </row>
@@ -1379,6 +1970,15 @@
         <v>18681.707</v>
       </c>
       <c r="D65" s="3" t="n">
+        <v>15280.288</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>17332.006</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>16509.439</v>
+      </c>
+      <c r="G65" s="3" t="n">
         <v>18681.707</v>
       </c>
     </row>
@@ -1393,6 +1993,15 @@
         <v>19549.432</v>
       </c>
       <c r="D66" s="3" t="n">
+        <v>16003.133</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>18163.196</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>17260.521</v>
+      </c>
+      <c r="G66" s="3" t="n">
         <v>19549.432</v>
       </c>
     </row>
@@ -1407,6 +2016,15 @@
         <v>20201.795</v>
       </c>
       <c r="D67" s="3" t="n">
+        <v>16535.809</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>18789.412</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>17809.194</v>
+      </c>
+      <c r="G67" s="3" t="n">
         <v>20201.795</v>
       </c>
     </row>
@@ -1421,6 +2039,15 @@
         <v>21039.791</v>
       </c>
       <c r="D68" s="3" t="n">
+        <v>17200.152</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>19590.203</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>18503.641</v>
+      </c>
+      <c r="G68" s="3" t="n">
         <v>21039.791</v>
       </c>
     </row>
@@ -1435,6 +2062,15 @@
         <v>22022.201</v>
       </c>
       <c r="D69" s="3" t="n">
+        <v>18018.127</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>20532.25</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>19357.855</v>
+      </c>
+      <c r="G69" s="3" t="n">
         <v>22022.201</v>
       </c>
     </row>
@@ -1449,6 +2085,15 @@
         <v>22494.315</v>
       </c>
       <c r="D70" s="3" t="n">
+        <v>18357.537</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>20962.069</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>19732.697</v>
+      </c>
+      <c r="G70" s="3" t="n">
         <v>22494.315</v>
       </c>
     </row>
@@ -1463,6 +2108,15 @@
         <v>23161.992</v>
       </c>
       <c r="D71" s="3" t="n">
+        <v>18816.627</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>21581.15</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>20226.414</v>
+      </c>
+      <c r="G71" s="3" t="n">
         <v>23161.992</v>
       </c>
     </row>
@@ -1477,6 +2131,15 @@
         <v>24066.902</v>
       </c>
       <c r="D72" s="3" t="n">
+        <v>19463.448</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>22433.416</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>20909.884</v>
+      </c>
+      <c r="G72" s="3" t="n">
         <v>24066.902</v>
       </c>
     </row>
@@ -1491,6 +2154,15 @@
         <v>25227.313</v>
       </c>
       <c r="D73" s="3" t="n">
+        <v>20346.871</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>23510.606</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>21860.443</v>
+      </c>
+      <c r="G73" s="3" t="n">
         <v>25227.313</v>
       </c>
     </row>
@@ -1505,6 +2177,15 @@
         <v>26423.854</v>
       </c>
       <c r="D74" s="3" t="n">
+        <v>21257.259</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>24623.772</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>22828.945</v>
+      </c>
+      <c r="G74" s="3" t="n">
         <v>26423.854</v>
       </c>
     </row>
@@ -1519,6 +2200,15 @@
         <v>27010.148</v>
       </c>
       <c r="D75" s="3" t="n">
+        <v>21477.166</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>25170.226</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>23065.608</v>
+      </c>
+      <c r="G75" s="3" t="n">
         <v>27010.148</v>
       </c>
     </row>
@@ -1533,6 +2223,15 @@
         <v>30051.849</v>
       </c>
       <c r="D76" s="3" t="n">
+        <v>24020.179</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>27985.443</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>25810.142</v>
+      </c>
+      <c r="G76" s="3" t="n">
         <v>30051.849</v>
       </c>
     </row>
@@ -1547,6 +2246,15 @@
         <v>33673.661</v>
       </c>
       <c r="D77" s="3" t="n">
+        <v>27015.61</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>31362.945</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>29024.39</v>
+      </c>
+      <c r="G77" s="3" t="n">
         <v>33673.661</v>
       </c>
     </row>
@@ -1561,6 +2269,15 @@
         <v>34771.025</v>
       </c>
       <c r="D78" s="3" t="n">
+        <v>27731.851</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>32429.654</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>29741.71</v>
+      </c>
+      <c r="G78" s="3" t="n">
         <v>34771.025</v>
       </c>
     </row>
@@ -1575,6 +2292,15 @@
         <v>35899.94</v>
       </c>
       <c r="D79" s="3" t="n">
+        <v>28430.946</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>33484.697</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>30476.126</v>
+      </c>
+      <c r="G79" s="3" t="n">
         <v>35899.94</v>
       </c>
     </row>
@@ -1589,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1628,7 +2354,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Productive Capital Stock (K*)</t>
+          <t>Productive Capital Stock (K*; BEA net current-cost, primary)</t>
         </is>
       </c>
     </row>
@@ -1801,40 +2527,56 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S517-EXFIN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | variant</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>S517-EXIPP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S517-EXBOTH</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S517 — Productive Capital Stock (K*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>**Chapter**: 5 supporting. **Period**: 1925-2024. **Units**: billions_usd.</t>
+          <t># S517 — Productive Capital Stock (K*)</t>
         </is>
       </c>
     </row>
@@ -1846,161 +2588,377 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 supporting. **Period**: 1925-2024. **Units**: billions_usd.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>K* is the productive constant capital STOCK — the accumulated past production that sits behind each year's productive activity. Distinguished from Mp (S502, constant capital FLOW = depreciation + materials used).</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K* is the productive constant capital STOCK — the accumulated past production that sits behind each year's productive activity. Distinguished from Mp (S502, constant capital FLOW = depreciation + materials used).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BEA Fixed Assets Table 4.1 (cached at `data/raw/bea/fixed_assets_4_1_net_stock.csv`), Line 1: "Private nonresidential fixed assets". 100 years (1925-2024).</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>## Productive partition note</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets Table 4.1 (cached at `data/raw/bea/fixed_assets_4_1_net_stock.csv`), Line 1: "Private nonresidential fixed assets". 100 years (1925-2024).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Line 1 is TOTAL private nonresidential fixed assets — includes both productive and a small unproductive (financial-sector real estate) component. Standard first-pass K*. A refinement (per IMPLEMENTATION_PLAN.md Phase 2.A) would subtract Line 33 (Financial sector, ~5-10% of total) to get a more faithful productive K*.</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>## Productive partition note</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>## Gross-vs-net disclosure (v1.1 Phase 5)</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Line 1 is TOTAL private nonresidential fixed assets — includes both productive and a small unproductive (financial-sector real estate) component. Standard first-pass K*. A refinement (per IMPLEMENTATION_PLAN.md Phase 2.A) would subtract Line 33 (Financial sector, ~5-10% of total) to get a more faithful productive K*.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>&gt; **Note**: ST 1994 prose calls K* "gross capital stock" (e.g., Table 5.8 header), but published values match BEA Fixed Assets Table 4.1 **NET** stock exactly at all 5 benchmark years (1948 = 292, 1958 = 551, 1967 = 871, 1980 = 3 800, 1989 = 6 700 $B). The book's terminology is in error; the implementation is net stock. BEA publishes no current-cost gross stock for private nonresidential fixed assets. See `Technical/DIVERGENCE_REGISTER.json` entry **DIV-008** for the full divergence record.</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>## Gross-vs-net + book-level disclosure (D2 / DIV-D01, corrected 2026-07-02)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>## Endpoints</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>&gt; **HEADLINE divergence (`DIV-D01`).** The earlier claim that the build "matches BEA NET stock,</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1948 = $292B, 1989 = $6,700B, 2024 = $35,900B. Validator PASS (range + monotonic).</t>
+          <t>&gt; so the book's 'gross' label is an error" is **half the story**. The KB v2 read of Table 5.8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>&gt; confirms the book's K* row is **"C\*_f = fixed nonresidential GROSS private capital" (BEA 1987</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>## Unblocks</t>
+          <t>&gt; vintage)**, with values **384.30 (1948), 710.90 (1958), 1093.00 (1967), 4225.20 (1979),</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>&gt; 8387.49 (1989)** — the book gross panel is at `data/source/book_tables/_panel_Kstar_gross_1948_1989.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S510 (K/V*), S513 (r*), S514 (r*_adj), and the activation of XS001 (Social Burden Rate).</t>
+          <t>&gt; The build's BEA net current-cost stock (292 / 551 / 871 / 3800 / 6700 $B) runs **20-24% BELOW**</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>&gt; the book's gross K* (the tautological match is between the build and its OWN net source, not the book).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>&gt;</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>&gt; **D2 empirical adjudication (G3, "focus on Shaikh-Tonak replication").** Among *constructible*</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
+        <is>
+          <t>&gt; variants, as-published NET is the **best** match to the book's own K* (mean abs dev 21.8% over</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>&gt; 1948-1989). Every productive-boundary "scrub" fits the book WORSE, because the book is gross</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>&gt; (above net) while scrubs cut net lower: ex-financial 24.5%, ex-IPP 26.2%, ex-both 28.9%. The</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>&gt; gross concept that would fit best is **not cleanly constructible** (BEA publishes no current-$</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>&gt; gross; FA Table 4.2 is a dimensionless quantity index and is not cached; the implied gross/net</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>&gt; ratio is non-constant and vintage-confounded) — so it is documented, not synthesized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>&gt; **Primary K* therefore stays as-published net; r* path is unchanged.** The scrub concepts are</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>&gt; published as clearly-labelled variant subseries. Supersedes DIV-008/DIV-027; patch:</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>&gt; `Handoffs/REVIEW_2026-07/D1_DIV_PATCHES.json`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>## Variant subseries (D2, NOT primary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- **S517-EXFIN** = (FA4.1 L1 − L33)/1000 — drops financial-industry fixed capital (productive/unproductive boundary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- **S517-EXIPP** = (FA4.1 L1 − L4)/1000 — drops all capitalized IPP (1999 software + 2013 R&amp;D/artistic revisions, backcast).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>- **S517-EXBOTH** = (FA4.1 L1 − L33 − L4 + L36)/1000 — most S&amp;T-faithful asset boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>These raise r* (smaller denominator) by +6.5% / +16.0% / +23.4% in 2024 relative terms but fit the</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>book's own K* LEVELS worse; the falling-rate result survives under all (see `CAPITAL_SCRUB_MEMO.md`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>## Endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1948 = $292B, 1989 = $6,700B, 2024 = $35,900B. Validator PASS (range + monotonic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>## Unblocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>S510 (K/V*), S513 (r*), S514 (r*_adj), and the activation of XS001 (Social Burden Rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -2389,7 +3347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2644,6 +3602,30 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>book_reference_values</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>{"1948": 384.3, "1958": 710.9, "1967": 1093.0, "1980": 4225.2, "1989": 8387.49}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>reference_values_note</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TAUTOLOGICAL (= loader output, BEA FA4.1 L1 net). The BOOK's Table 5.8 gross K* is 384.30/710.90/1093.00/4225.20/8387.49 at 1948/58/67/79/89 - net runs 20-24% below (DIV-D01, headline). Book gross panel: data/source/book_tables/_panel_Kstar_gross_1948_1989.csv.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S517.xlsx
+++ b/extenbooks/S517.xlsx
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5 (The Marxian Categories: Empirical Estimates), Appendix H (K* net stock of fixed capital, text-only in published volume)", "shaikh_appendix_ref": "Appendix H tabulated K* endpoints (Appendix H is text-only per RMWND CLAUDE.md and is not extracted in the current KB build); cross-reference Table 5.8 / 5.9 (K* = C*f reporting convention, billions of current dollars) and Figures 5.5 and 5.8 (K* plotted in r* construction)", "extension_source": "BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock; pre-cached at Inputs/ST2/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: Inputs/ST2/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)", "extension_url": "https://apps.bea.gov/iTable/?reqid=10&amp;step=2&amp;isuri=1 (Fixed Assets, Table 4.1); API endpoint: https://apps.bea.gov/api/data?UserID=&lt;KEY&gt;&amp;method=GetData&amp;datasetname=FixedAssets&amp;TableName=FAAt401&amp;Frequency=A&amp;Year=ALL&amp;ResultFormat=JSON", "conceptual_continuity": "Productive Capital Stock K* is the current-cost net stock of fixed capital deployed in the productive economy. Both the book period (1948-1989) and the extension (1990-2024) draw on the same BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, Current-Cost Net Stock) \u2014 i.e., the underlying source series is identical across the seam. The splice is therefore trivial: splice_method=level at 1989 with rescale_factor=1.0, because there is no series-change discontinuity to bridge. The only methodological caveat (shared with the book period itself) is that Table 4.1 Line 1 is aggregate private nonresidential \u2014 it is not yet filtered through the 85-IO productive concordance to subtract the financial-sector component (estimated ~5-10%). This concordance refinement is a future Stage 5 task (see IMPLEMENTATION_PLAN.md Phase 2.A); for now the aggregate is used in both eras, which preserves comparability across the splice but biases the level upward relative to a strict productive subset.", "vintage_note": "BEA API pull dated 2026-02-24 (per Inputs/ST2/Inputs/API_Data/BEA/provenance_fixed_assets.json). Book-period reference values are frozen at the book's publication vintage in principle, but the operational book reference for S517 is the same modern BEA Table 4.1 series used for the extension (because the book's Appendix H values are not yet extracted from the text-only appendix). BEA Fixed Assets undergoes periodic comprehensive revisions; the cached 2026-02-24 pull represents the most recent vintage at the time of construction. For strict gross-stock replication (book Table 5.8 specifies K* = gross stock), BEA Table 4.2 (Current-Cost Gross Stock) would be the alternative source; not yet pulled.", "note": "Stage 5 cohort 3 extension patch per Decision 0003 binary-invariant rule. Book and extension share the same source, making this a degenerate-but-honest level splice (rescale_factor=1.0)."}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5 (The Marxian Categories: Empirical Estimates), Appendix H (K* net stock of fixed capital, text-only in published volume)", "shaikh_appendix_ref": "Appendix H tabulated K* endpoints (Appendix H is text-only per RMWND CLAUDE.md and is not extracted in the current KB build); cross-reference Table 5.8 / 5.9 (K* = C*f reporting convention, billions of current dollars) and Figures 5.5 and 5.8 (K* plotted in r* construction)", "extension_source": "BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock; pre-cached at data/raw/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)", "extension_url": "https://apps.bea.gov/iTable/?reqid=10&amp;step=2&amp;isuri=1 (Fixed Assets, Table 4.1); API endpoint: https://apps.bea.gov/api/data?UserID=&lt;KEY&gt;&amp;method=GetData&amp;datasetname=FixedAssets&amp;TableName=FAAt401&amp;Frequency=A&amp;Year=ALL&amp;ResultFormat=JSON", "conceptual_continuity": "Productive Capital Stock K* is the current-cost net stock of fixed capital deployed in the productive economy. Both the book period (1948-1989) and the extension (1990-2024) draw on the same BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, Current-Cost Net Stock) \u2014 i.e., the underlying source series is identical across the seam. The splice is therefore trivial: splice_method=level at 1989 with rescale_factor=1.0, because there is no series-change discontinuity to bridge. The only methodological caveat (shared with the book period itself) is that Table 4.1 Line 1 is aggregate private nonresidential \u2014 it is not yet filtered through the 85-IO productive concordance to subtract the financial-sector component (estimated ~5-10%). This concordance refinement is a future Stage 5 task (see IMPLEMENTATION_PLAN.md Phase 2.A); for now the aggregate is used in both eras, which preserves comparability across the splice but biases the level upward relative to a strict productive subset.", "vintage_note": "BEA API pull dated 2026-02-24 (per data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json). Book-period reference values are frozen at the book's publication vintage in principle, but the operational book reference for S517 is the same modern BEA Table 4.1 series used for the extension (because the book's Appendix H values are not yet extracted from the text-only appendix). BEA Fixed Assets undergoes periodic comprehensive revisions; the cached 2026-02-24 pull represents the most recent vintage at the time of construction. For strict gross-stock replication (book Table 5.8 specifies K* = gross stock), BEA Table 4.2 (Current-Cost Gross Stock) would be the alternative source; not yet pulled.", "note": "Stage 5 cohort 3 extension patch per Decision 0003 binary-invariant rule. Book and extension share the same source, making this a degenerate-but-honest level splice (rescale_factor=1.0)."}</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock — pre-cached at Inputs/ST2/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: Inputs/ST2/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)</t>
+          <t>BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock — pre-cached at data/raw/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S517.xlsx
+++ b/extenbooks/S517.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -457,6 +457,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +496,11 @@
           <t>BEA, units=billions_usd</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 Table 5.8 (C*_f, 'BEA 1987' gross vintage), units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -530,6 +536,11 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>S517-EXT</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>S517-GROSS-A</t>
         </is>
       </c>
     </row>
@@ -555,6 +566,9 @@
       <c r="G3" s="3" t="n">
         <v/>
       </c>
+      <c r="H3" s="3" t="n">
+        <v>384.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -578,6 +592,9 @@
       <c r="G4" s="3" t="n">
         <v/>
       </c>
+      <c r="H4" s="3" t="n">
+        <v>400.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -601,6 +618,9 @@
       <c r="G5" s="3" t="n">
         <v/>
       </c>
+      <c r="H5" s="3" t="n">
+        <v>438.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -624,6 +644,9 @@
       <c r="G6" s="3" t="n">
         <v/>
       </c>
+      <c r="H6" s="3" t="n">
+        <v>480.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -647,6 +670,9 @@
       <c r="G7" s="3" t="n">
         <v/>
       </c>
+      <c r="H7" s="3" t="n">
+        <v>506.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -670,6 +696,9 @@
       <c r="G8" s="3" t="n">
         <v/>
       </c>
+      <c r="H8" s="3" t="n">
+        <v>526.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -693,6 +722,9 @@
       <c r="G9" s="3" t="n">
         <v/>
       </c>
+      <c r="H9" s="3" t="n">
+        <v>546.2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -716,6 +748,9 @@
       <c r="G10" s="3" t="n">
         <v/>
       </c>
+      <c r="H10" s="3" t="n">
+        <v>591.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -739,6 +774,9 @@
       <c r="G11" s="3" t="n">
         <v/>
       </c>
+      <c r="H11" s="3" t="n">
+        <v>650.3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -762,6 +800,9 @@
       <c r="G12" s="3" t="n">
         <v/>
       </c>
+      <c r="H12" s="3" t="n">
+        <v>689.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -785,6 +826,9 @@
       <c r="G13" s="3" t="n">
         <v/>
       </c>
+      <c r="H13" s="3" t="n">
+        <v>710.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -808,6 +852,9 @@
       <c r="G14" s="3" t="n">
         <v/>
       </c>
+      <c r="H14" s="3" t="n">
+        <v>738</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -831,6 +878,9 @@
       <c r="G15" s="3" t="n">
         <v/>
       </c>
+      <c r="H15" s="3" t="n">
+        <v>755.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -854,6 +904,9 @@
       <c r="G16" s="3" t="n">
         <v/>
       </c>
+      <c r="H16" s="3" t="n">
+        <v>775.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -877,6 +930,9 @@
       <c r="G17" s="3" t="n">
         <v/>
       </c>
+      <c r="H17" s="3" t="n">
+        <v>802.3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -900,6 +956,9 @@
       <c r="G18" s="3" t="n">
         <v/>
       </c>
+      <c r="H18" s="3" t="n">
+        <v>832</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -923,6 +982,9 @@
       <c r="G19" s="3" t="n">
         <v/>
       </c>
+      <c r="H19" s="3" t="n">
+        <v>872.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -946,6 +1008,9 @@
       <c r="G20" s="3" t="n">
         <v/>
       </c>
+      <c r="H20" s="3" t="n">
+        <v>932.3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -969,6 +1034,9 @@
       <c r="G21" s="3" t="n">
         <v/>
       </c>
+      <c r="H21" s="3" t="n">
+        <v>1014.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -992,6 +1060,9 @@
       <c r="G22" s="3" t="n">
         <v/>
       </c>
+      <c r="H22" s="3" t="n">
+        <v>1093</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1015,6 +1086,9 @@
       <c r="G23" s="3" t="n">
         <v/>
       </c>
+      <c r="H23" s="3" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1038,6 +1112,9 @@
       <c r="G24" s="3" t="n">
         <v/>
       </c>
+      <c r="H24" s="3" t="n">
+        <v>1320.9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1061,6 +1138,9 @@
       <c r="G25" s="3" t="n">
         <v/>
       </c>
+      <c r="H25" s="3" t="n">
+        <v>1453.4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1084,6 +1164,9 @@
       <c r="G26" s="3" t="n">
         <v/>
       </c>
+      <c r="H26" s="3" t="n">
+        <v>1598.9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1107,6 +1190,9 @@
       <c r="G27" s="3" t="n">
         <v/>
       </c>
+      <c r="H27" s="3" t="n">
+        <v>1737.7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1130,6 +1216,9 @@
       <c r="G28" s="3" t="n">
         <v/>
       </c>
+      <c r="H28" s="3" t="n">
+        <v>1940.3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1153,6 +1242,9 @@
       <c r="G29" s="3" t="n">
         <v/>
       </c>
+      <c r="H29" s="3" t="n">
+        <v>2387.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1176,6 +1268,9 @@
       <c r="G30" s="3" t="n">
         <v/>
       </c>
+      <c r="H30" s="3" t="n">
+        <v>2661.7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1199,6 +1294,9 @@
       <c r="G31" s="3" t="n">
         <v/>
       </c>
+      <c r="H31" s="3" t="n">
+        <v>2920.8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1222,6 +1320,9 @@
       <c r="G32" s="3" t="n">
         <v/>
       </c>
+      <c r="H32" s="3" t="n">
+        <v>3253.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1245,6 +1346,9 @@
       <c r="G33" s="3" t="n">
         <v/>
       </c>
+      <c r="H33" s="3" t="n">
+        <v>3774.6</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1268,6 +1372,9 @@
       <c r="G34" s="3" t="n">
         <v/>
       </c>
+      <c r="H34" s="3" t="n">
+        <v>4225.2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1291,6 +1398,9 @@
       <c r="G35" s="3" t="n">
         <v/>
       </c>
+      <c r="H35" s="3" t="n">
+        <v>4844.4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1314,6 +1424,9 @@
       <c r="G36" s="3" t="n">
         <v/>
       </c>
+      <c r="H36" s="3" t="n">
+        <v>5503.7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1337,6 +1450,9 @@
       <c r="G37" s="3" t="n">
         <v/>
       </c>
+      <c r="H37" s="3" t="n">
+        <v>5859.2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1360,6 +1476,9 @@
       <c r="G38" s="3" t="n">
         <v/>
       </c>
+      <c r="H38" s="3" t="n">
+        <v>6094.71</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1383,6 +1502,9 @@
       <c r="G39" s="3" t="n">
         <v/>
       </c>
+      <c r="H39" s="3" t="n">
+        <v>6432.91</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1406,6 +1528,9 @@
       <c r="G40" s="3" t="n">
         <v/>
       </c>
+      <c r="H40" s="3" t="n">
+        <v>6706.44</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1429,6 +1554,9 @@
       <c r="G41" s="3" t="n">
         <v/>
       </c>
+      <c r="H41" s="3" t="n">
+        <v>7056.52</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1452,6 +1580,9 @@
       <c r="G42" s="3" t="n">
         <v/>
       </c>
+      <c r="H42" s="3" t="n">
+        <v>7459.32</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1475,6 +1606,9 @@
       <c r="G43" s="3" t="n">
         <v/>
       </c>
+      <c r="H43" s="3" t="n">
+        <v>7895.58</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1498,6 +1632,9 @@
       <c r="G44" s="3" t="n">
         <v/>
       </c>
+      <c r="H44" s="3" t="n">
+        <v>8387.49</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1521,6 +1658,9 @@
       <c r="G45" s="3" t="n">
         <v>7071.254</v>
       </c>
+      <c r="H45" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1544,6 +1684,9 @@
       <c r="G46" s="3" t="n">
         <v>7242.497</v>
       </c>
+      <c r="H46" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1567,6 +1710,9 @@
       <c r="G47" s="3" t="n">
         <v>7487.351</v>
       </c>
+      <c r="H47" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1590,6 +1736,9 @@
       <c r="G48" s="3" t="n">
         <v>7838.125</v>
       </c>
+      <c r="H48" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1613,6 +1762,9 @@
       <c r="G49" s="3" t="n">
         <v>8273.204</v>
       </c>
+      <c r="H49" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1636,6 +1788,9 @@
       <c r="G50" s="3" t="n">
         <v>8723.558000000001</v>
       </c>
+      <c r="H50" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1659,6 +1814,9 @@
       <c r="G51" s="3" t="n">
         <v>9152.132</v>
       </c>
+      <c r="H51" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1682,6 +1840,9 @@
       <c r="G52" s="3" t="n">
         <v>9674.473</v>
       </c>
+      <c r="H52" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1705,6 +1866,9 @@
       <c r="G53" s="3" t="n">
         <v>10226.721</v>
       </c>
+      <c r="H53" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1728,6 +1892,9 @@
       <c r="G54" s="3" t="n">
         <v>10849.249</v>
       </c>
+      <c r="H54" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1751,6 +1918,9 @@
       <c r="G55" s="3" t="n">
         <v>11607.864</v>
       </c>
+      <c r="H55" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1774,6 +1944,9 @@
       <c r="G56" s="3" t="n">
         <v>12189.396</v>
       </c>
+      <c r="H56" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1797,6 +1970,9 @@
       <c r="G57" s="3" t="n">
         <v>12616.326</v>
       </c>
+      <c r="H57" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1820,6 +1996,9 @@
       <c r="G58" s="3" t="n">
         <v>13038.217</v>
       </c>
+      <c r="H58" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1843,6 +2022,9 @@
       <c r="G59" s="3" t="n">
         <v>14152.545</v>
       </c>
+      <c r="H59" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1866,6 +2048,9 @@
       <c r="G60" s="3" t="n">
         <v>15429.476</v>
       </c>
+      <c r="H60" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1889,6 +2074,9 @@
       <c r="G61" s="3" t="n">
         <v>16706.002</v>
       </c>
+      <c r="H61" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1912,6 +2100,9 @@
       <c r="G62" s="3" t="n">
         <v>17647.597</v>
       </c>
+      <c r="H62" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1935,6 +2126,9 @@
       <c r="G63" s="3" t="n">
         <v>18787.982</v>
       </c>
+      <c r="H63" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1958,6 +2152,9 @@
       <c r="G64" s="3" t="n">
         <v>18233.843</v>
       </c>
+      <c r="H64" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1981,6 +2178,9 @@
       <c r="G65" s="3" t="n">
         <v>18681.707</v>
       </c>
+      <c r="H65" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2004,6 +2204,9 @@
       <c r="G66" s="3" t="n">
         <v>19549.432</v>
       </c>
+      <c r="H66" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2027,6 +2230,9 @@
       <c r="G67" s="3" t="n">
         <v>20201.795</v>
       </c>
+      <c r="H67" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2050,6 +2256,9 @@
       <c r="G68" s="3" t="n">
         <v>21039.791</v>
       </c>
+      <c r="H68" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2073,6 +2282,9 @@
       <c r="G69" s="3" t="n">
         <v>22022.201</v>
       </c>
+      <c r="H69" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2096,6 +2308,9 @@
       <c r="G70" s="3" t="n">
         <v>22494.315</v>
       </c>
+      <c r="H70" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2119,6 +2334,9 @@
       <c r="G71" s="3" t="n">
         <v>23161.992</v>
       </c>
+      <c r="H71" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2142,6 +2360,9 @@
       <c r="G72" s="3" t="n">
         <v>24066.902</v>
       </c>
+      <c r="H72" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2165,6 +2386,9 @@
       <c r="G73" s="3" t="n">
         <v>25227.313</v>
       </c>
+      <c r="H73" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2188,6 +2412,9 @@
       <c r="G74" s="3" t="n">
         <v>26423.854</v>
       </c>
+      <c r="H74" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2211,6 +2438,9 @@
       <c r="G75" s="3" t="n">
         <v>27010.148</v>
       </c>
+      <c r="H75" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2234,6 +2464,9 @@
       <c r="G76" s="3" t="n">
         <v>30051.849</v>
       </c>
+      <c r="H76" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2257,6 +2490,9 @@
       <c r="G77" s="3" t="n">
         <v>33673.661</v>
       </c>
+      <c r="H77" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2280,6 +2516,9 @@
       <c r="G78" s="3" t="n">
         <v>34771.025</v>
       </c>
+      <c r="H78" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2302,6 +2541,9 @@
       </c>
       <c r="G79" s="3" t="n">
         <v>35899.94</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2315,7 +2557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2563,144 +2805,148 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S517-GROSS-A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 Table 5.8 (C*_f, 'BEA 1987' gross vintage) | variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t># S517 — Productive Capital Stock (K*)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t># S517 — Productive Capital Stock (K*)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>**Chapter**: 5 supporting. **Period**: 1925-2024. **Units**: billions_usd.</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 supporting. **Period**: 1925-2024. **Units**: billions_usd.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>K* is the productive constant capital STOCK — the accumulated past production that sits behind each year's productive activity. Distinguished from Mp (S502, constant capital FLOW = depreciation + materials used).</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>K* is the productive constant capital STOCK — the accumulated past production that sits behind each year's productive activity. Distinguished from Mp (S502, constant capital FLOW = depreciation + materials used).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>BEA Fixed Assets Table 4.1 (cached at `data/raw/bea/fixed_assets_4_1_net_stock.csv`), Line 1: "Private nonresidential fixed assets". 100 years (1925-2024).</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BEA Fixed Assets Table 4.1 (cached at `data/raw/bea/fixed_assets_4_1_net_stock.csv`), Line 1: "Private nonresidential fixed assets". 100 years (1925-2024).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>## Productive partition note</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>## Productive partition note</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Line 1 is TOTAL private nonresidential fixed assets — includes both productive and a small unproductive (financial-sector real estate) component. Standard first-pass K*. A refinement (per IMPLEMENTATION_PLAN.md Phase 2.A) would subtract Line 33 (Financial sector, ~5-10% of total) to get a more faithful productive K*.</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Line 1 is TOTAL private nonresidential fixed assets — includes both productive and a small unproductive (financial-sector real estate) component. Standard first-pass K*. A refinement (per IMPLEMENTATION_PLAN.md Phase 2.A) would subtract Line 33 (Financial sector, ~5-10% of total) to get a more faithful productive K*.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>## Gross-vs-net + book-level disclosure (D2 / DIV-D01, corrected 2026-07-02)</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>## Gross-vs-net + book-level disclosure (D2 / DIV-D01, corrected 2026-07-02)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>&gt; **HEADLINE divergence (`DIV-D01`).** The earlier claim that the build "matches BEA NET stock,</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>&gt; so the book's 'gross' label is an error" is **half the story**. The KB v2 read of Table 5.8</t>
+          <t>&gt; **HEADLINE divergence (`DIV-D01`).** The earlier claim that the build "matches BEA NET stock,</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2954,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>&gt; confirms the book's K* row is **"C\*_f = fixed nonresidential GROSS private capital" (BEA 1987</t>
+          <t>&gt; so the book's 'gross' label is an error" is **half the story**. The KB v2 read of Table 5.8</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2962,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>&gt; vintage)**, with values **384.30 (1948), 710.90 (1958), 1093.00 (1967), 4225.20 (1979),</t>
+          <t>&gt; confirms the book's K* row is **"C\*_f = fixed nonresidential GROSS private capital" (BEA 1987</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2970,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>&gt; 8387.49 (1989)** — the book gross panel is at `data/source/book_tables/_panel_Kstar_gross_1948_1989.csv`.</t>
+          <t>&gt; vintage)**, with values **384.30 (1948), 710.90 (1958), 1093.00 (1967), 4225.20 (1979),</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2978,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>&gt; The build's BEA net current-cost stock (292 / 551 / 871 / 3800 / 6700 $B) runs **20-24% BELOW**</t>
+          <t>&gt; 8387.49 (1989)** — the book gross panel is at `data/source/book_tables/_panel_Kstar_gross_1948_1989.csv`.</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2986,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>&gt; the book's gross K* (the tautological match is between the build and its OWN net source, not the book).</t>
+          <t>&gt; The build's BEA net current-cost stock (292 / 551 / 871 / 3800 / 6700 $B) runs **20-24% BELOW**</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2994,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>&gt;</t>
+          <t>&gt; the book's gross K* (the tautological match is between the build and its OWN net source, not the book).</t>
         </is>
       </c>
     </row>
@@ -2756,7 +3002,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>&gt; **D2 empirical adjudication (G3, "focus on Shaikh-Tonak replication").** Among *constructible*</t>
+          <t>&gt;</t>
         </is>
       </c>
     </row>
@@ -2764,7 +3010,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>&gt; variants, as-published NET is the **best** match to the book's own K* (mean abs dev 21.8% over</t>
+          <t>&gt; **D2 empirical adjudication (G3, "focus on Shaikh-Tonak replication").** Among *constructible*</t>
         </is>
       </c>
     </row>
@@ -2772,7 +3018,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>&gt; 1948-1989). Every productive-boundary "scrub" fits the book WORSE, because the book is gross</t>
+          <t>&gt; variants, as-published NET is the **best** match to the book's own K* (mean abs dev 21.8% over</t>
         </is>
       </c>
     </row>
@@ -2780,7 +3026,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>&gt; (above net) while scrubs cut net lower: ex-financial 24.5%, ex-IPP 26.2%, ex-both 28.9%. The</t>
+          <t>&gt; 1948-1989). Every productive-boundary "scrub" fits the book WORSE, because the book is gross</t>
         </is>
       </c>
     </row>
@@ -2788,7 +3034,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>&gt; gross concept that would fit best is **not cleanly constructible** (BEA publishes no current-$</t>
+          <t>&gt; (above net) while scrubs cut net lower: ex-financial 24.5%, ex-IPP 26.2%, ex-both 28.9%. The</t>
         </is>
       </c>
     </row>
@@ -2796,7 +3042,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>&gt; gross; FA Table 4.2 is a dimensionless quantity index and is not cached; the implied gross/net</t>
+          <t>&gt; gross concept that would fit best is **not cleanly constructible** (BEA publishes no current-$</t>
         </is>
       </c>
     </row>
@@ -2804,7 +3050,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>&gt; ratio is non-constant and vintage-confounded) — so it is documented, not synthesized.</t>
+          <t>&gt; gross; FA Table 4.2 is a dimensionless quantity index and is not cached; the implied gross/net</t>
         </is>
       </c>
     </row>
@@ -2812,7 +3058,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>&gt; **Primary K* therefore stays as-published net; r* path is unchanged.** The scrub concepts are</t>
+          <t>&gt; ratio is non-constant and vintage-confounded) — so it is documented, not synthesized.</t>
         </is>
       </c>
     </row>
@@ -2820,7 +3066,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>&gt; published as clearly-labelled variant subseries. Supersedes DIV-008/DIV-027; patch:</t>
+          <t>&gt; **Primary K* therefore stays as-published net; r* path is unchanged.** The scrub concepts are</t>
         </is>
       </c>
     </row>
@@ -2828,39 +3074,39 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>&gt; `Handoffs/REVIEW_2026-07/D1_DIV_PATCHES.json`.</t>
+          <t>&gt; published as clearly-labelled variant subseries. Supersedes DIV-008/DIV-027; patch:</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>&gt; `Handoffs/REVIEW_2026-07/D1_DIV_PATCHES.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>## Variant subseries (D2, NOT primary)</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>## Variant subseries (D2, NOT primary)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>- **S517-EXFIN** = (FA4.1 L1 − L33)/1000 — drops financial-industry fixed capital (productive/unproductive boundary).</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>- **S517-EXIPP** = (FA4.1 L1 − L4)/1000 — drops all capitalized IPP (1999 software + 2013 R&amp;D/artistic revisions, backcast).</t>
+          <t>- **S517-EXFIN** = (FA4.1 L1 − L33)/1000 — drops financial-industry fixed capital (productive/unproductive boundary).</t>
         </is>
       </c>
     </row>
@@ -2868,99 +3114,143 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- **S517-EXBOTH** = (FA4.1 L1 − L33 − L4 + L36)/1000 — most S&amp;T-faithful asset boundary.</t>
+          <t>- **S517-EXIPP** = (FA4.1 L1 − L4)/1000 — drops all capitalized IPP (1999 software + 2013 R&amp;D/artistic revisions, backcast).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- **S517-EXBOTH** = (FA4.1 L1 − L33 − L4 + L36)/1000 — most S&amp;T-faithful asset boundary.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>These raise r* (smaller denominator) by +6.5% / +16.0% / +23.4% in 2024 relative terms but fit the</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>book's own K* LEVELS worse; the falling-rate result survives under all (see `CAPITAL_SCRUB_MEMO.md`).</t>
+          <t>These raise r* (smaller denominator) by +6.5% / +16.0% / +23.4% in 2024 relative terms but fit the</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>book's own K* LEVELS worse; the falling-rate result survives under all (see `CAPITAL_SCRUB_MEMO.md`).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>## Endpoints</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>## Endpoints</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1948 = $292B, 1989 = $6,700B, 2024 = $35,900B. Validator PASS (range + monotonic).</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1948 = $292B, 1989 = $6,700B, 2024 = $35,900B. Validator PASS (range + monotonic).</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>## Unblocks</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>## Unblocks</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>S510 (K/V*), S513 (r*), S514 (r*_adj), and the activation of XS001 (Social Burden Rate).</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>S510 (K/V*), S513 (r*), S514 (r*_adj), and the activation of XS001 (Social Burden Rate).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>## Book-period Gross-K* variant (added 2026-07-07, K-plan WP-K4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>**Subseries `S517-GROSS-A`** (book period 1948-1989 only, `nan` beyond). Book Table 5.8 GROSS K* (C*_f), loaded via L01 from the in-tree gross panel. The book-faithful capital axis; the primary net S517-A runs ~21.8% below it. Gives the r*/r*' family its first INDEPENDENT (non-tautological) book anchor. See `VPR_S517_gross_book` in the registry, `DIVERGENCE_REGISTER.json` **DIV-070** (+ narrowed **DIV-058**), and `Handoffs/REVIEW_2026-07-07/F2_KSTAR_FIDELITY.md`. Additive only — the primary net series is unchanged; current-$ gross is non-constructible 1990-&gt; (BEA discontinued current-cost gross at the 1997 revision), so there is no extension.</t>
         </is>
       </c>
     </row>
@@ -3347,10 +3637,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -3401,228 +3691,281 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S517-GROSS-A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BEA</t>
-        </is>
-      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BEA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>output_subseries</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S517-EXT</t>
+          <t>level</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>combined_subseries</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S517-COMBINED</t>
+          <t>S517-EXT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rescale_factor</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>S517-COMBINED</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>extension_period</t>
+          <t>rescale_factor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1990, 2024]</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>extension_period</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5 (The Marxian Categories: Empirical Estimates), Appendix H (K* net stock of fixed capital, text-only in published volume)", "shaikh_appendix_ref": "Appendix H tabulated K* endpoints (Appendix H is text-only per RMWND CLAUDE.md and is not extracted in the current KB build); cross-reference Table 5.8 / 5.9 (K* = C*f reporting convention, billions of current dollars) and Figures 5.5 and 5.8 (K* plotted in r* construction)", "extension_source": "BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock; pre-cached at data/raw/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)", "extension_url": "https://apps.bea.gov/iTable/?reqid=10&amp;step=2&amp;isuri=1 (Fixed Assets, Table 4.1); API endpoint: https://apps.bea.gov/api/data?UserID=&lt;KEY&gt;&amp;method=GetData&amp;datasetname=FixedAssets&amp;TableName=FAAt401&amp;Frequency=A&amp;Year=ALL&amp;ResultFormat=JSON", "conceptual_continuity": "Productive Capital Stock K* is the current-cost net stock of fixed capital deployed in the productive economy. Both the book period (1948-1989) and the extension (1990-2024) draw on the same BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, Current-Cost Net Stock) \u2014 i.e., the underlying source series is identical across the seam. The splice is therefore trivial: splice_method=level at 1989 with rescale_factor=1.0, because there is no series-change discontinuity to bridge. The only methodological caveat (shared with the book period itself) is that Table 4.1 Line 1 is aggregate private nonresidential \u2014 it is not yet filtered through the 85-IO productive concordance to subtract the financial-sector component (estimated ~5-10%). This concordance refinement is a future Stage 5 task (see IMPLEMENTATION_PLAN.md Phase 2.A); for now the aggregate is used in both eras, which preserves comparability across the splice but biases the level upward relative to a strict productive subset.", "vintage_note": "BEA API pull dated 2026-02-24 (per data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json). Book-period reference values are frozen at the book's publication vintage in principle, but the operational book reference for S517 is the same modern BEA Table 4.1 series used for the extension (because the book's Appendix H values are not yet extracted from the text-only appendix). BEA Fixed Assets undergoes periodic comprehensive revisions; the cached 2026-02-24 pull represents the most recent vintage at the time of construction. For strict gross-stock replication (book Table 5.8 specifies K* = gross stock), BEA Table 4.2 (Current-Cost Gross Stock) would be the alternative source; not yet pulled.", "note": "Stage 5 cohort 3 extension patch per Decision 0003 binary-invariant rule. Book and extension share the same source, making this a degenerate-but-honest level splice (rescale_factor=1.0)."}</t>
+          <t>[1990, 2024]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5 (The Marxian Categories: Empirical Estimates), Appendix H (K* net stock of fixed capital, text-only in published volume)", "shaikh_appendix_ref": "Appendix H tabulated K* endpoints (Appendix H is text-only per RMWND CLAUDE.md and is not extracted in the current KB build); cross-reference Table 5.8 / 5.9 (K* = C*f reporting convention, billions of current dollars) and Figures 5.5 and 5.8 (K* plotted in r* construction)", "extension_source": "BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock; pre-cached at data/raw/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)", "extension_url": "https://apps.bea.gov/iTable/?reqid=10&amp;step=2&amp;isuri=1 (Fixed Assets, Table 4.1); API endpoint: https://apps.bea.gov/api/data?UserID=&lt;KEY&gt;&amp;method=GetData&amp;datasetname=FixedAssets&amp;TableName=FAAt401&amp;Frequency=A&amp;Year=ALL&amp;ResultFormat=JSON", "conceptual_continuity": "Productive Capital Stock K* is the current-cost net stock of fixed capital deployed in the productive economy. Both the book period (1948-1989) and the extension (1990-2024) draw on the same BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets, Current-Cost Net Stock) \u2014 i.e., the underlying source series is identical across the seam. The splice is therefore trivial: splice_method=level at 1989 with rescale_factor=1.0, because there is no series-change discontinuity to bridge. The only methodological caveat (shared with the book period itself) is that Table 4.1 Line 1 is aggregate private nonresidential \u2014 it is not yet filtered through the 85-IO productive concordance to subtract the financial-sector component (estimated ~5-10%). This concordance refinement is a future Stage 5 task (see IMPLEMENTATION_PLAN.md Phase 2.A); for now the aggregate is used in both eras, which preserves comparability across the splice but biases the level upward relative to a strict productive subset.", "vintage_note": "BEA API pull dated 2026-02-24 (per data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json). Book-period reference values are frozen at the book's publication vintage in principle, but the operational book reference for S517 is the same modern BEA Table 4.1 series used for the extension (because the book's Appendix H values are not yet extracted from the text-only appendix). BEA Fixed Assets undergoes periodic comprehensive revisions; the cached 2026-02-24 pull represents the most recent vintage at the time of construction. For strict gross-stock replication (book Table 5.8 specifies K* = gross stock), BEA Table 4.2 (Current-Cost Gross Stock) would be the alternative source; not yet pulled.", "note": "Stage 5 cohort 3 extension patch per Decision 0003 binary-invariant rule. Book and extension share the same source, making this a degenerate-but-honest level splice (rescale_factor=1.0)."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>depends_on</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{"1948": 291.557, "1958": 551.356, "1967": 871.188, "1980": 3800.29, "1989": 6699.84}</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>v1.3_patch</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIV-027: removed the spurious 1925 benchmark (126.977). S517 covers 1948+ on NET stock; the series never produces a 1925 value, so the benchmark was always MISSING. All 5 in-range anchors PASS. NET-vs-gross K* convention switch deferred to v1.4 (not changed here).</t>
+          <t>{"1948": 291.557, "1958": 551.356, "1967": 871.188, "1980": 3800.29, "1989": 6699.84}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>v1.3_patch</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[100.0, 20000.0]</t>
+          <t>DIV-027: removed the spurious 1925 benchmark (126.977). S517 covers 1948+ on NET stock; the series never produces a 1925 value, so the benchmark was always MISSING. All 5 in-range anchors PASS. NET-vs-gross K* convention switch deferred to v1.4 (not changed here).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reference_values_units</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>billions of current dollars (current-cost net stock)</t>
+          <t>[100.0, 20000.0]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>reference_values_source</t>
+          <t>reference_values_units</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock — pre-cached at data/raw/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)</t>
+          <t>billions of current dollars (current-cost net stock)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>extension_year_range</t>
+          <t>reference_values_source</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1948, 2024]</t>
+          <t>BEA Fixed Assets Table 4.1 Line 1 (Private nonresidential fixed assets), Current-Cost Net Stock — pre-cached at data/raw/Inputs/API_Data/BEA/fixed_assets_4_1_net_stock.csv (provenance: data/raw/Inputs/API_Data/BEA/provenance_fixed_assets.json; BEA API pull dated 2026-02-24)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>book_reference_values</t>
+          <t>extension_year_range</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{"1948": 384.3, "1958": 710.9, "1967": 1093.0, "1980": 4225.2, "1989": 8387.49}</t>
+          <t>[1948, 2024]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>book_reference_values</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>{"1948": 384.3, "1958": 710.9, "1967": 1093.0, "1980": 4844.4, "1989": 8387.49}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>book_reference_values_1980_fix</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-07 (K-plan WP-K2): 1980 book gross K* corrected 4225.2 -&gt; 4844.40. 4225.20 is the book Table 5.8 1979 value (mislabeled under key 1980); true 1980 = 4844.40. VERIFIED against KB v2 5.8 (F1b spot-verify) and the in-tree gross panel _panel_Kstar_gross_1948_1989.csv (1979=4225.2, 1980=4844.4). Not read by V03 (S517 V03 uses validation.reference_values, the net anchors); label-fidelity fix only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>reference_values_note</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TAUTOLOGICAL (= loader output, BEA FA4.1 L1 net). The BOOK's Table 5.8 gross K* is 384.30/710.90/1093.00/4225.20/8387.49 at 1948/58/67/79/89 - net runs 20-24% below (DIV-D01, headline). Book gross panel: data/source/book_tables/_panel_Kstar_gross_1948_1989.csv.</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S517-A refvals are TAUTOLOGICAL (= loader output, BEA FA4.1 L1 net). The BOOK's Table 5.8 GROSS K* is 384.30 (1948) / 710.90 (1958) / 1093.00 (1967) / 4225.20 (1979) / 4844.40 (1980) / 8387.49 (1989) - net runs ~21.8% below (DIV-058, headline). The book-faithful gross axis is now materialized as the S517-GROSS-A variant (validation.variant_reference_values), giving the r*/r*' family its first INDEPENDENT book anchor (A1 de-tautologization). Book gross panel: data/source/book_tables/_panel_Kstar_gross_1948_1989.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>variant_reference_values</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{"S517-GROSS-A": {"1948": 384.3, "1949": 400.2, "1950": 438.7, "1951": 480.8, "1952": 506.2, "1953": 526.6, "1954": 546.2, "1955": 591.2, "1956": 650.3, "1957": 689.7, "1958": 710.9, "1959": 738.0, "1960": 755.7, "1961": 775.4, "1962": 802.3, "1963": 832.0, "1964": 872.3, "1965": 932.3, "1966": 1014.4, "1967": 1093.0, "1968": 1202.5, "1969": 1320.9, "1970": 1453.4, "1971": 1598.9, "1972": 1737.7, "1973": 1940.3, "1974": 2387.1, "1975": 2661.7, "1976": 2920.8, "1977": 3253.5, "1978": 3774.6, "1979": 4225.2, "1980": 4844.4, "1981": 5503.7, "1982": 5859.2, "1983": 6094.71, "1984": 6432.91, "1985": 6706.44, "1986": 7056.52, "1987": 7459.32, "1988": 7895.58, "1989": 8387.49}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>variant_reference_values_note</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S517-GROSS-A = book Table 5.8 GROSS K* (C*_f), the book's own printed cells (1948=384.30 .. 1989=8387.49). Exact by construction (the variant IS the book panel). Book-anchored INDEPENDENT reference values (printed book Table 5.8 / 5.7 / 5.11 cells, KB v2 _combined/5.8.csv; full 1948-1989 column). Checked by V03 against the S*-GROSS-A book-faithful variant. Unlike validation.reference_values (tautological = loader output, A1), these are the book's OWN published numbers -&gt; the r*/r*' family's first independent book anchor (F2 2026-07-07, K-plan WP-K3).</t>
         </is>
       </c>
     </row>
